--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17418,7 +17418,7 @@
         </is>
       </c>
       <c r="E28" s="106" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F28" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E28/CONFIGURACIÓN!$C$10,1))</f>

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17286,7 +17286,7 @@
         </is>
       </c>
       <c r="E24" s="106" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F24" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E24/CONFIGURACIÓN!$C$10,1))</f>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="E25" s="106" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F25" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E25/CONFIGURACIÓN!$C$10,1))</f>
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="E26" s="106" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F26" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E26/CONFIGURACIÓN!$C$10,1))</f>
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="E27" s="106" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F27" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E27/CONFIGURACIÓN!$C$10,1))</f>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="E30" s="106" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E30/CONFIGURACIÓN!$C$10,1))</f>

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="E29" s="106" t="n">
-        <v>7000</v>
+        <v>8060</v>
       </c>
       <c r="F29" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E29/CONFIGURACIÓN!$C$10,1))</f>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="E30" s="106" t="n">
-        <v>5000</v>
+        <v>5940</v>
       </c>
       <c r="F30" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E30/CONFIGURACIÓN!$C$10,1))</f>

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -16926,7 +16926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H32"/>
+  <dimension ref="B1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="150" min="1" max="1"/>
@@ -17268,6 +17268,24 @@
           <t>Especie</t>
         </is>
       </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Meta Volteo
+(m³SSC)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Meta Madereo
+(m³SSC)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Meta Clasificado
+(m³SSC)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="150">
       <c r="B24" s="103" t="inlineStr">
@@ -17301,6 +17319,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I24" s="106"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="150">
       <c r="B25" s="103" t="inlineStr">
@@ -17334,6 +17355,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="150">
       <c r="B26" s="103" t="inlineStr">
@@ -17367,6 +17391,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="150">
       <c r="B27" s="103" t="inlineStr">
@@ -17400,6 +17427,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106"/>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="150">
       <c r="B28" s="103" t="inlineStr">
@@ -17433,6 +17463,9 @@
           <t>EUGL</t>
         </is>
       </c>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="106"/>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="150">
       <c r="B29" s="103" t="inlineStr">
@@ -17466,6 +17499,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="106"/>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="150">
       <c r="B30" s="103" t="inlineStr">
@@ -17499,6 +17535,9 @@
           <t>PIRA</t>
         </is>
       </c>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="150">
       <c r="B31" s="103" t="inlineStr">
@@ -17532,6 +17571,9 @@
           <t>EUGL</t>
         </is>
       </c>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="150">
       <c r="B32" s="255" t="inlineStr">

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17319,9 +17319,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
+      <c r="I24" s="106" t="n">
+        <v>9443</v>
+      </c>
+      <c r="J24" s="106" t="n">
+        <v>8962</v>
+      </c>
+      <c r="K24" s="106" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="150">
       <c r="B25" s="103" t="inlineStr">
@@ -17355,9 +17361,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
+      <c r="I25" s="106" t="n">
+        <v>8681</v>
+      </c>
+      <c r="J25" s="106" t="n">
+        <v>8454</v>
+      </c>
+      <c r="K25" s="106" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="150">
       <c r="B26" s="103" t="inlineStr">
@@ -17391,9 +17403,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
+      <c r="I26" s="106" t="n">
+        <v>9035</v>
+      </c>
+      <c r="J26" s="106" t="n">
+        <v>8690</v>
+      </c>
+      <c r="K26" s="106" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="150">
       <c r="B27" s="103" t="inlineStr">
@@ -17427,9 +17445,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
+      <c r="I27" s="106" t="n">
+        <v>8870</v>
+      </c>
+      <c r="J27" s="106" t="n">
+        <v>8580</v>
+      </c>
+      <c r="K27" s="106" t="n">
+        <v>8000</v>
+      </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="150">
       <c r="B28" s="103" t="inlineStr">
@@ -17463,9 +17487,15 @@
           <t>EUGL</t>
         </is>
       </c>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
+      <c r="I28" s="106" t="n">
+        <v>7762</v>
+      </c>
+      <c r="J28" s="106" t="n">
+        <v>7508</v>
+      </c>
+      <c r="K28" s="106" t="n">
+        <v>7000</v>
+      </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="150">
       <c r="B29" s="103" t="inlineStr">
@@ -17499,9 +17529,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
+      <c r="I29" s="106" t="n">
+        <v>8855</v>
+      </c>
+      <c r="J29" s="106" t="n">
+        <v>8590</v>
+      </c>
+      <c r="K29" s="106" t="n">
+        <v>8060</v>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="150">
       <c r="B30" s="103" t="inlineStr">
@@ -17535,9 +17571,15 @@
           <t>PIRA</t>
         </is>
       </c>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
+      <c r="I30" s="106" t="n">
+        <v>6441</v>
+      </c>
+      <c r="J30" s="106" t="n">
+        <v>6274</v>
+      </c>
+      <c r="K30" s="106" t="n">
+        <v>5940</v>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="150">
       <c r="B31" s="103" t="inlineStr">
@@ -17571,9 +17613,15 @@
           <t>EUGL</t>
         </is>
       </c>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
+      <c r="I31" s="106" t="n">
+        <v>6675</v>
+      </c>
+      <c r="J31" s="106" t="n">
+        <v>6450</v>
+      </c>
+      <c r="K31" s="106" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="150">
       <c r="B32" s="255" t="inlineStr">

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17556,7 +17556,7 @@
         </is>
       </c>
       <c r="E30" s="106" t="n">
-        <v>5940</v>
+        <v>10000</v>
       </c>
       <c r="F30" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E30/CONFIGURACIÓN!$C$10,1))</f>
@@ -17572,13 +17572,13 @@
         </is>
       </c>
       <c r="I30" s="106" t="n">
-        <v>6441</v>
+        <v>10501</v>
       </c>
       <c r="J30" s="106" t="n">
-        <v>6274</v>
+        <v>10334</v>
       </c>
       <c r="K30" s="106" t="n">
-        <v>5940</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="150">

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="I30" s="106" t="n">
-        <v>10501</v>
+        <v>10939</v>
       </c>
       <c r="J30" s="106" t="n">
-        <v>10334</v>
+        <v>10626</v>
       </c>
       <c r="K30" s="106" t="n">
         <v>10000</v>

--- a/Dashboard_CosechaForestal.xlsx
+++ b/Dashboard_CosechaForestal.xlsx
@@ -17304,7 +17304,7 @@
         </is>
       </c>
       <c r="E24" s="106" t="n">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F24" s="107">
         <f>IF(CONFIGURACIÓN!$C$10=0,0,ROUND(E24/CONFIGURACIÓN!$C$10,1))</f>
@@ -17320,13 +17320,13 @@
         </is>
       </c>
       <c r="I24" s="106" t="n">
-        <v>9443</v>
+        <v>21608</v>
       </c>
       <c r="J24" s="106" t="n">
-        <v>8962</v>
+        <v>21072</v>
       </c>
       <c r="K24" s="106" t="n">
-        <v>8000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="150">
